--- a/config/ecu_config.xlsx
+++ b/config/ecu_config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\REDO\CODINGTOOL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\REDO\CODINGTOOL\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2193FA2A-92E8-4E0E-A6B3-1AEAF530500E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A67018-F573-4F93-AA82-C0B429CFAA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{19663F63-6748-4EB2-A277-B57ED0772D29}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{19663F63-6748-4EB2-A277-B57ED0772D29}"/>
   </bookViews>
   <sheets>
     <sheet name="ECU_list" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>ECU</t>
   </si>
@@ -36,12 +36,6 @@
     <t>RespID</t>
   </si>
   <si>
-    <t>ACM</t>
-  </si>
-  <si>
-    <t>BCM</t>
-  </si>
-  <si>
     <t>EPS</t>
   </si>
   <si>
@@ -63,18 +57,12 @@
     <t>62C</t>
   </si>
   <si>
-    <t>2IN1</t>
-  </si>
-  <si>
     <t>6BD</t>
   </si>
   <si>
     <t>63D</t>
   </si>
   <si>
-    <t>EDS</t>
-  </si>
-  <si>
     <t>69B</t>
   </si>
   <si>
@@ -90,9 +78,6 @@
     <t>MHU</t>
   </si>
   <si>
-    <t>XGW</t>
-  </si>
-  <si>
     <t>AVAS</t>
   </si>
   <si>
@@ -102,9 +87,6 @@
     <t>62A</t>
   </si>
   <si>
-    <t>ABS</t>
-  </si>
-  <si>
     <t>6A9</t>
   </si>
   <si>
@@ -121,6 +103,123 @@
   </si>
   <si>
     <t>6FF</t>
+  </si>
+  <si>
+    <t>CCU</t>
+  </si>
+  <si>
+    <t>6BE</t>
+  </si>
+  <si>
+    <t>63E</t>
+  </si>
+  <si>
+    <t>PDU_OBC</t>
+  </si>
+  <si>
+    <t>BCM_FR</t>
+  </si>
+  <si>
+    <t>DSCU</t>
+  </si>
+  <si>
+    <t>69E</t>
+  </si>
+  <si>
+    <t>61E</t>
+  </si>
+  <si>
+    <t>ETG</t>
+  </si>
+  <si>
+    <t>68E</t>
+  </si>
+  <si>
+    <t>60E</t>
+  </si>
+  <si>
+    <t>EVCC</t>
+  </si>
+  <si>
+    <t>69F</t>
+  </si>
+  <si>
+    <t>61F</t>
+  </si>
+  <si>
+    <t>FCAM</t>
+  </si>
+  <si>
+    <t>MRR</t>
+  </si>
+  <si>
+    <t>6A5</t>
+  </si>
+  <si>
+    <t>OCS</t>
+  </si>
+  <si>
+    <t>6C4</t>
+  </si>
+  <si>
+    <t>SRR_RL</t>
+  </si>
+  <si>
+    <t>6B7</t>
+  </si>
+  <si>
+    <t>SRR_RR</t>
+  </si>
+  <si>
+    <t>6B6</t>
+  </si>
+  <si>
+    <t>TBOX</t>
+  </si>
+  <si>
+    <t>68A</t>
+  </si>
+  <si>
+    <t>60A</t>
+  </si>
+  <si>
+    <t>USS_FR</t>
+  </si>
+  <si>
+    <t>6B2</t>
+  </si>
+  <si>
+    <t>USS_RR</t>
+  </si>
+  <si>
+    <t>6B1</t>
+  </si>
+  <si>
+    <t>6CC</t>
+  </si>
+  <si>
+    <t>DKCU</t>
+  </si>
+  <si>
+    <t>64C</t>
+  </si>
+  <si>
+    <t>BCM | BCM_FL</t>
+  </si>
+  <si>
+    <t>ACM | ACU</t>
+  </si>
+  <si>
+    <t>2IN1 | POD</t>
+  </si>
+  <si>
+    <t>EDS | MCU</t>
+  </si>
+  <si>
+    <t>XGW | CVC</t>
+  </si>
+  <si>
+    <t>ABS | WCBS</t>
   </si>
 </sst>
 </file>
@@ -165,7 +264,38 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -475,10 +605,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{818DC715-4C26-4E39-9E0F-AC55699BF4CF}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="17.109375" style="1" customWidth="1"/>
+    <col min="2" max="3" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -494,7 +625,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="B2" s="1">
         <v>688</v>
@@ -505,7 +636,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="B3" s="1">
         <v>681</v>
@@ -516,10 +647,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C4" s="1">
         <v>628</v>
@@ -527,7 +658,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1">
         <v>690</v>
@@ -538,7 +669,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1">
         <v>693</v>
@@ -549,43 +680,43 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1">
         <v>675</v>
@@ -593,7 +724,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1">
         <v>684</v>
@@ -604,7 +735,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="B12" s="1">
         <v>682</v>
@@ -615,21 +746,21 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C14" s="1">
         <v>629</v>
@@ -637,27 +768,201 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1">
         <v>0</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1">
+        <v>689</v>
+      </c>
+      <c r="C17" s="1">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="1">
+        <v>686</v>
+      </c>
+      <c r="C19" s="1">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="B20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="1">
+        <v>696</v>
+      </c>
+      <c r="C23" s="1">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="1">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="1">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="1">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="1">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="1">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="1">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>58</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/config/ecu_config.xlsx
+++ b/config/ecu_config.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\REDO\CODINGTOOL\config\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9566F2BA-2917-488B-BF93-441CEF1C8C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="ECU_list"/>
+    <sheet name="ECU_list" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
   <si>
     <t>ECU</t>
   </si>
@@ -37,9 +43,6 @@
     <t>6A8</t>
   </si>
   <si>
-    <t>StallSwitch</t>
-  </si>
-  <si>
     <t>BMS</t>
   </si>
   <si>
@@ -52,18 +55,12 @@
     <t>62C</t>
   </si>
   <si>
-    <t>2IN1 | POD</t>
-  </si>
-  <si>
     <t>6BD</t>
   </si>
   <si>
     <t>63D</t>
   </si>
   <si>
-    <t>EDS | MCU</t>
-  </si>
-  <si>
     <t>69B</t>
   </si>
   <si>
@@ -76,12 +73,6 @@
     <t>6F5</t>
   </si>
   <si>
-    <t>MHU</t>
-  </si>
-  <si>
-    <t>XGW | CVC</t>
-  </si>
-  <si>
     <t>AVAS</t>
   </si>
   <si>
@@ -91,9 +82,6 @@
     <t>62A</t>
   </si>
   <si>
-    <t>ABS | WCBS</t>
-  </si>
-  <si>
     <t>6A9</t>
   </si>
   <si>
@@ -112,12 +100,6 @@
     <t>6FF</t>
   </si>
   <si>
-    <t>CCU</t>
-  </si>
-  <si>
-    <t>PDU_OBC</t>
-  </si>
-  <si>
     <t>6BE</t>
   </si>
   <si>
@@ -127,9 +109,6 @@
     <t>BCM_FR</t>
   </si>
   <si>
-    <t>DSCU</t>
-  </si>
-  <si>
     <t>69E</t>
   </si>
   <si>
@@ -145,21 +124,12 @@
     <t>60E</t>
   </si>
   <si>
-    <t>EVCC</t>
-  </si>
-  <si>
     <t>69F</t>
   </si>
   <si>
     <t>61F</t>
   </si>
   <si>
-    <t>FCAM</t>
-  </si>
-  <si>
-    <t>MRR</t>
-  </si>
-  <si>
     <t>6A5</t>
   </si>
   <si>
@@ -196,9 +166,6 @@
     <t>6B2</t>
   </si>
   <si>
-    <t>USS_RR</t>
-  </si>
-  <si>
     <t>6B1</t>
   </si>
   <si>
@@ -209,13 +176,258 @@
   </si>
   <si>
     <t>64C</t>
+  </si>
+  <si>
+    <t>XGW | CVC |IVC</t>
+  </si>
+  <si>
+    <t>6FB</t>
+  </si>
+  <si>
+    <t>67B</t>
+  </si>
+  <si>
+    <t>BPM</t>
+  </si>
+  <si>
+    <t>6A6</t>
+  </si>
+  <si>
+    <t>6AD</t>
+  </si>
+  <si>
+    <t>62D</t>
+  </si>
+  <si>
+    <t>6C0</t>
+  </si>
+  <si>
+    <t>6C1</t>
+  </si>
+  <si>
+    <t>APM</t>
+  </si>
+  <si>
+    <t>DCDC 2</t>
+  </si>
+  <si>
+    <t>68D</t>
+  </si>
+  <si>
+    <t>60D</t>
+  </si>
+  <si>
+    <t>HUD</t>
+  </si>
+  <si>
+    <t>6BF</t>
+  </si>
+  <si>
+    <t>63F</t>
+  </si>
+  <si>
+    <t>POD_GW</t>
+  </si>
+  <si>
+    <t>6C2</t>
+  </si>
+  <si>
+    <t>6B5</t>
+  </si>
+  <si>
+    <t>SRR_FL</t>
+  </si>
+  <si>
+    <t>6B4</t>
+  </si>
+  <si>
+    <t>SRR_FR</t>
+  </si>
+  <si>
+    <t>ABS | WCBS |ESC|IDB</t>
+  </si>
+  <si>
+    <t>BSD|ADAS1</t>
+  </si>
+  <si>
+    <t>6A7</t>
+  </si>
+  <si>
+    <t>FCAM|SCAM</t>
+  </si>
+  <si>
+    <t>68F</t>
+  </si>
+  <si>
+    <t>60F</t>
+  </si>
+  <si>
+    <t>YSS</t>
+  </si>
+  <si>
+    <t>MRR|MRGEN</t>
+  </si>
+  <si>
+    <t>6B9</t>
+  </si>
+  <si>
+    <t>SRR_RR_M</t>
+  </si>
+  <si>
+    <t>6AF</t>
+  </si>
+  <si>
+    <t>62F</t>
+  </si>
+  <si>
+    <t>CPD</t>
+  </si>
+  <si>
+    <t>CCU|CCU_F</t>
+  </si>
+  <si>
+    <t>SHVU|SHVU_F</t>
+  </si>
+  <si>
+    <t>69A</t>
+  </si>
+  <si>
+    <t>61A</t>
+  </si>
+  <si>
+    <t>EDS_R</t>
+  </si>
+  <si>
+    <t>6C3</t>
+  </si>
+  <si>
+    <t>SHVU_R</t>
+  </si>
+  <si>
+    <t>6B0</t>
+  </si>
+  <si>
+    <t>PAS_LITE 2</t>
+  </si>
+  <si>
+    <t>ADAS2|PAS_LITE 1|PAS</t>
+  </si>
+  <si>
+    <t>EDS | MCU |FMCU|EDS_F</t>
+  </si>
+  <si>
+    <t>AMP</t>
+  </si>
+  <si>
+    <t>6AE</t>
+  </si>
+  <si>
+    <t>62E</t>
+  </si>
+  <si>
+    <t>EASC</t>
+  </si>
+  <si>
+    <t>OBC1</t>
+  </si>
+  <si>
+    <t>PDU|OBC2</t>
+  </si>
+  <si>
+    <t>6AB</t>
+  </si>
+  <si>
+    <t>62B</t>
+  </si>
+  <si>
+    <t>EPS2</t>
+  </si>
+  <si>
+    <t>6BB</t>
+  </si>
+  <si>
+    <t>63B</t>
+  </si>
+  <si>
+    <t>TRM</t>
+  </si>
+  <si>
+    <t>DSCU|PSM_D|PSM_A</t>
+  </si>
+  <si>
+    <t>ASU</t>
+  </si>
+  <si>
+    <t>ASU_G</t>
+  </si>
+  <si>
+    <t>6C9</t>
+  </si>
+  <si>
+    <t>LDM_L</t>
+  </si>
+  <si>
+    <t>6CA</t>
+  </si>
+  <si>
+    <t>64A</t>
+  </si>
+  <si>
+    <t>LDM_R</t>
+  </si>
+  <si>
+    <t>CCU_R|CCH</t>
+  </si>
+  <si>
+    <t>SS|GS|EKS2</t>
+  </si>
+  <si>
+    <t>USS_RR |EKS 1</t>
+  </si>
+  <si>
+    <t>MHU|IVI</t>
+  </si>
+  <si>
+    <t>6C6</t>
+  </si>
+  <si>
+    <t>PTC</t>
+  </si>
+  <si>
+    <t>RCU|WCBS_R</t>
+  </si>
+  <si>
+    <t>2IN1 | POD | PDU|DCDC1|DCCO_DCDC</t>
+  </si>
+  <si>
+    <t>6CB</t>
+  </si>
+  <si>
+    <t>64B</t>
+  </si>
+  <si>
+    <t>DCCO_DCFC</t>
+  </si>
+  <si>
+    <t>EVCC|DCCO_EVCC</t>
+  </si>
+  <si>
+    <t>68B</t>
+  </si>
+  <si>
+    <t>60B</t>
+  </si>
+  <si>
+    <t>IPC 1</t>
+  </si>
+  <si>
+    <t>IPC 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -226,7 +438,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -259,28 +471,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -291,10 +517,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -332,71 +558,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -424,7 +650,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -447,11 +673,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -460,13 +686,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -476,7 +702,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -485,7 +711,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -494,7 +720,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -502,10 +728,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -570,360 +796,703 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C62"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="3" width="17.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="8.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="8.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="24.77734375" style="4" customWidth="1"/>
+    <col min="2" max="3" width="8.88671875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>688</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>608</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>681</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>601</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>628</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="1">
+        <v>690</v>
+      </c>
+      <c r="C5" s="1">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2">
-        <v>690</v>
-      </c>
-      <c r="C5" s="2">
-        <v>610</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1">
+        <v>693</v>
+      </c>
+      <c r="C6" s="1">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2">
-        <v>693</v>
-      </c>
-      <c r="C6" s="2">
-        <v>613</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="1" t="s">
+    <row r="10" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C10" s="1">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="1">
+        <v>684</v>
+      </c>
+      <c r="C11" s="1">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="1">
+        <v>682</v>
+      </c>
+      <c r="C12" s="1">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="2">
-        <v>675</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="1" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="2">
-        <v>684</v>
-      </c>
-      <c r="C11" s="2">
-        <v>604</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="1" t="s">
+      <c r="C14" s="1">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="2">
-        <v>682</v>
-      </c>
-      <c r="C12" s="2">
-        <v>602</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="2" t="s">
+    </row>
+    <row r="16" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="1" t="s">
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="2" t="s">
+    </row>
+    <row r="17" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="1">
+        <v>689</v>
+      </c>
+      <c r="C17" s="1">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="2">
-        <v>629</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="2" t="s">
+    </row>
+    <row r="19" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="B19" s="1">
+        <v>686</v>
+      </c>
+      <c r="C19" s="1">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="2">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2" t="s">
+    </row>
+    <row r="21" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="2">
-        <v>689</v>
-      </c>
-      <c r="C17" s="2">
-        <v>609</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="2" t="s">
+    </row>
+    <row r="22" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="1" t="s">
+    <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="1">
+        <v>696</v>
+      </c>
+      <c r="C23" s="1">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="2">
-        <v>686</v>
-      </c>
-      <c r="C19" s="2">
-        <v>606</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="1" t="s">
+      <c r="C24" s="1">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C25" s="1">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C26" s="1">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="1" t="s">
+      <c r="C27" s="1">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="1" t="s">
+    <row r="29" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="2">
-        <v>696</v>
-      </c>
-      <c r="C23" s="2">
-        <v>616</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C29" s="1">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="2">
-        <v>625</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="1" t="s">
+      <c r="C30" s="1">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="2">
-        <v>644</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="2">
-        <v>637</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="1" t="s">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="2">
-        <v>636</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="2" t="s">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C33" s="2">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="2" t="s">
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B35" s="2">
+        <v>683</v>
+      </c>
+      <c r="C35" s="2">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="2">
-        <v>632</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="1" t="s">
+      <c r="C36" s="2">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="2">
-        <v>631</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="2" t="s">
+      <c r="C37" s="2">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>64</v>
       </c>
     </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="2">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="2">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="2">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" s="2">
+        <v>697</v>
+      </c>
+      <c r="C43" s="2">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="2">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C46" s="2">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" s="2">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" s="2">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" s="2">
+        <v>685</v>
+      </c>
+      <c r="C51" s="2">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" s="2">
+        <v>694</v>
+      </c>
+      <c r="C54" s="2">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B56" s="2">
+        <v>695</v>
+      </c>
+      <c r="C56" s="2">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B57" s="2">
+        <v>691</v>
+      </c>
+      <c r="C57" s="2">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C58" s="2">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C60" s="2">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="B1:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/config/ecu_config.xlsx
+++ b/config/ecu_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\REDO\CODINGTOOL\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9566F2BA-2917-488B-BF93-441CEF1C8C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4E8B6C-596C-4C44-9F21-E8335DFC2F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ECU_list" sheetId="1" r:id="rId1"/>

--- a/config/ecu_config.xlsx
+++ b/config/ecu_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\REDO\SW\EEIV Diagnostic_v1.0.0\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB999EC-A825-4126-8240-B6AC58D4B199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D11CAB-13CE-44B2-8601-72665D217728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ECU_list" sheetId="1" r:id="rId1"/>
@@ -262,21 +262,12 @@
     <t>|VCU|</t>
   </si>
   <si>
-    <t>|2IN1|POD|PDU|DCDC1|DCCO_DCDC|</t>
-  </si>
-  <si>
     <t>|EDS|MCU|FMCU|EDS_F|</t>
   </si>
   <si>
     <t>|EAC|</t>
   </si>
   <si>
-    <t>|MHU|IVI|</t>
-  </si>
-  <si>
-    <t>|XGW|CVC|IVC|</t>
-  </si>
-  <si>
     <t>|AVAS|</t>
   </si>
   <si>
@@ -331,12 +322,6 @@
     <t>|USS_RR |EKS_1|</t>
   </si>
   <si>
-    <t>|DKCU|</t>
-  </si>
-  <si>
-    <t>|BPM|</t>
-  </si>
-  <si>
     <t>|DCDC_2|</t>
   </si>
   <si>
@@ -428,6 +413,21 @@
   </si>
   <si>
     <t>|BAS|</t>
+  </si>
+  <si>
+    <t>|BPM|BCM_BPM|</t>
+  </si>
+  <si>
+    <t>|2IN1|POD|PDU|DCDC1|DCCO_DCDC|3IN1|</t>
+  </si>
+  <si>
+    <t>|XGW|CVC|IVC|IVC_SGC</t>
+  </si>
+  <si>
+    <t>|MHU|IVI|IVC_MHU|</t>
+  </si>
+  <si>
+    <t>|VDKCU|</t>
   </si>
 </sst>
 </file>
@@ -892,7 +892,7 @@
     </row>
     <row r="8" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="9" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="10" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>10</v>
@@ -925,7 +925,7 @@
     </row>
     <row r="11" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="B11" s="1">
         <v>684</v>
@@ -936,7 +936,7 @@
     </row>
     <row r="12" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>84</v>
+        <v>133</v>
       </c>
       <c r="B12" s="1">
         <v>682</v>
@@ -947,7 +947,7 @@
     </row>
     <row r="13" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>11</v>
@@ -958,7 +958,7 @@
     </row>
     <row r="14" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>13</v>
@@ -969,7 +969,7 @@
     </row>
     <row r="15" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>14</v>
@@ -980,7 +980,7 @@
     </row>
     <row r="16" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B16" s="1">
         <v>0</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="17" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B17" s="1">
         <v>689</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="18" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>17</v>
@@ -1013,7 +1013,7 @@
     </row>
     <row r="19" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B19" s="1">
         <v>686</v>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="20" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>19</v>
@@ -1035,7 +1035,7 @@
     </row>
     <row r="21" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>21</v>
@@ -1046,7 +1046,7 @@
     </row>
     <row r="22" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>23</v>
@@ -1057,7 +1057,7 @@
     </row>
     <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B23" s="1">
         <v>696</v>
@@ -1068,7 +1068,7 @@
     </row>
     <row r="24" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>25</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="25" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>26</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="26" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>27</v>
@@ -1101,7 +1101,7 @@
     </row>
     <row r="27" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>28</v>
@@ -1112,7 +1112,7 @@
     </row>
     <row r="28" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>29</v>
@@ -1123,7 +1123,7 @@
     </row>
     <row r="29" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>31</v>
@@ -1134,7 +1134,7 @@
     </row>
     <row r="30" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>32</v>
@@ -1145,7 +1145,7 @@
     </row>
     <row r="31" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>33</v>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>35</v>
@@ -1167,7 +1167,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>37</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>38</v>
@@ -1189,7 +1189,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B35" s="2">
         <v>683</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>40</v>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>41</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>42</v>
@@ -1233,7 +1233,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>44</v>
@@ -1244,7 +1244,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>46</v>
@@ -1255,7 +1255,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>47</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>48</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B43" s="2">
         <v>697</v>
@@ -1288,7 +1288,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>49</v>
@@ -1299,7 +1299,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>50</v>
@@ -1310,7 +1310,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>52</v>
@@ -1321,7 +1321,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>53</v>
@@ -1332,7 +1332,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>55</v>
@@ -1343,7 +1343,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>57</v>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>58</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B51" s="2">
         <v>685</v>
@@ -1376,7 +1376,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>59</v>
@@ -1387,7 +1387,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>61</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B54" s="2">
         <v>694</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>63</v>
@@ -1420,7 +1420,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B56" s="2">
         <v>695</v>
@@ -1431,7 +1431,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B57" s="2">
         <v>691</v>
@@ -1442,7 +1442,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>65</v>
@@ -1453,7 +1453,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>66</v>
@@ -1464,7 +1464,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>68</v>
@@ -1475,7 +1475,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>69</v>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>71</v>
@@ -1497,7 +1497,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>73</v>
